--- a/artfynd/A 12199-2026 artfynd.xlsx
+++ b/artfynd/A 12199-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131885398</v>
       </c>
       <c r="B2" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12199-2026 artfynd.xlsx
+++ b/artfynd/A 12199-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131885398</v>
       </c>
       <c r="B2" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12199-2026 artfynd.xlsx
+++ b/artfynd/A 12199-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131885398</v>
+        <v>63181410</v>
       </c>
       <c r="B2" t="n">
-        <v>57137</v>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 12199, Mosjön, Tyllinge, Sm</t>
+          <t>Tyllinge, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565079</v>
+        <v>565247</v>
       </c>
       <c r="R2" t="n">
-        <v>6430777</v>
+        <v>6430645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +764,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2011-07-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2011-07-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,15 +784,498 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>63201129</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>565247</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6430645</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lokal-ID: 16  Box-ID: 16F</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131885398</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 12199, Mosjön, Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565079</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6430777</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>63189313</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565247</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6430645</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>lokal-ID: 16  Box-ID: 16F</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>63229020</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tyllinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565247</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6430645</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-07-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>lokal-ID: 16  Box-ID: 16F</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
